--- a/www/download/IND.surplus_value.empe.r.pc.zdW13.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>0.857621209435145</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>80.38</t>
+          <t>0.803790688271896</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>0.873758880284802</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>84.72</t>
+          <t>0.847165280280337</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>76.02</t>
+          <t>0.76016593911907</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>83.51</t>
+          <t>0.835082686938926</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>87.42</t>
+          <t>0.874231621733476</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79.23</t>
+          <t>0.792273511139493</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>0.680970679204478</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>0.462815048232958</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>0.393182247402936</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>0.425380280854332</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>0.397268388237351</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>0.532573262970996</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0.599972950608747</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>0.217139843731504</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>0.264555296011286</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>0.494220010259993</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>0.468705327964571</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>44.72</t>
+          <t>0.447199513935227</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>51.56</t>
+          <t>0.515630167693138</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>0.483410003249767</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>0.473473342516439</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>0.346527960850208</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>0.289599694539368</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>0.269375145927475</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>0.245001030046358</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>0.245385781857681</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>0.207595483708119</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>0.28928687468258</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-0.0886051839236751</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-0.113248519459742</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-0.0713834182981848</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-0.0666623308383421</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-14.98</t>
+          <t>-0.149793372290852</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-0.171561352361221</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-22.18</t>
+          <t>-0.221785701072929</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.2</t>
+          <t>-0.282001131259109</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-41.6</t>
+          <t>-0.416024519885219</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-44.45</t>
+          <t>-0.44450795038576</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-43.4</t>
+          <t>-0.434014844224709</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-42.66</t>
+          <t>-0.426598034137371</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-39.58</t>
+          <t>-0.395768540713735</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-33.77</t>
+          <t>-0.337660589285953</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-37.85</t>
+          <t>-0.378454709634137</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>309.89</t>
+          <t>3.09888456920238</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>360.5</t>
+          <t>3.60501293409479</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>418.55</t>
+          <t>4.18545622895827</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>315.31</t>
+          <t>3.15310172653198</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>357.92</t>
+          <t>3.57918824262452</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>374.31</t>
+          <t>3.74314020103878</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>366.38</t>
+          <t>3.66375074919754</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>380.27</t>
+          <t>3.80269309811919</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>377.58</t>
+          <t>3.7757901527541</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>386.21</t>
+          <t>3.86209463711832</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>403.77</t>
+          <t>4.03773243202701</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>421.7</t>
+          <t>4.21696833890572</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>405.53</t>
+          <t>4.05526078516649</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>371.82</t>
+          <t>3.71820257428149</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>327.51</t>
+          <t>3.27513257333647</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>236.79</t>
+          <t>2.36791626519861</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>240.66</t>
+          <t>2.40663355866759</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>260.34</t>
+          <t>2.60342683066998</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>257.8</t>
+          <t>2.57800132395624</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>294.35</t>
+          <t>2.94345000970706</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>311.56</t>
+          <t>3.11561901104618</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>330.69</t>
+          <t>3.3069465156086</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>350.35</t>
+          <t>3.50345619679462</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>358.13</t>
+          <t>3.58126367703482</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>352.37</t>
+          <t>3.5236802668521</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>331.54</t>
+          <t>3.31541830709538</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>324.38</t>
+          <t>3.24380646008357</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>318.57</t>
+          <t>3.18570828769141</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>302.5</t>
+          <t>3.02504343712252</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>306.3</t>
+          <t>3.06303376532686</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>108.67</t>
+          <t>1.08670021429773</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>117.61</t>
+          <t>1.1760836103355</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>132.22</t>
+          <t>1.32219303910011</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>116.27</t>
+          <t>1.16272119051075</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>106.64</t>
+          <t>1.06636469558396</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>0.892826773830411</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>0.776198373185008</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.24</t>
+          <t>0.77235322731003</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>65.59</t>
+          <t>0.655862807100743</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>0.600650154357257</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>0.484358581128745</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>0.43237658348899</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>0.4966299112047</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>51.48</t>
+          <t>0.514822635701061</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>0.652615455110828</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-22.14</t>
+          <t>-0.221434172643992</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-0.190473962938112</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-0.167577908907944</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-0.139479644207825</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-0.0959263347767534</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-0.0380187891517342</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.0434901056130015</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>0.109336938131574</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>0.179555015415608</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>0.245371945356613</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>0.310619258511174</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>0.352587450030988</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>49.48</t>
+          <t>0.494817701318855</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>0.513431262853195</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>55.83</t>
+          <t>0.558281854060263</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>112.86</t>
+          <t>1.12858650234561</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>1.06039147766413</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>1.38527177064386</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>1.29201075485338</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>110.62</t>
+          <t>1.10619610525558</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>1.14403464630617</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>96.11</t>
+          <t>0.961086328313987</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92.21</t>
+          <t>0.922066582396341</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>0.70373762241301</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>0.766537159607055</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>0.798827472045682</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>82.38</t>
+          <t>0.823791584143308</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>101.89</t>
+          <t>1.01893257348018</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>0.702308723181498</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>1.03637236616875</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>422.33</t>
+          <t>4.22332267099386</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>270.07</t>
+          <t>2.70066166620186</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>308.59</t>
+          <t>3.08590092239735</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>293.49</t>
+          <t>2.93494785517161</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>294.05</t>
+          <t>2.94047197423435</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>306.64</t>
+          <t>3.0664202301305</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>272.22</t>
+          <t>2.72221740407199</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>257.67</t>
+          <t>2.57672265932468</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>222.52</t>
+          <t>2.22521052497336</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>197.82</t>
+          <t>1.97820554059631</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>187.41</t>
+          <t>1.87408216807123</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>197.76</t>
+          <t>1.9775575094665</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>191.18</t>
+          <t>1.9117928302558</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>178.98</t>
+          <t>1.78984156083672</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>217.86</t>
+          <t>2.17864662302988</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.0215572843503791</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>0.126569768257979</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>0.288223881061056</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>0.247815197787071</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>0.217578511202642</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>0.152786731533638</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>0.176981404274808</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>0.181347476825025</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.0175188816279079</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.000896776251537501</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.0436364489694054</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>0.0404817774330326</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.0184821037438883</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>0.0241297843684503</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>0.0595804033846421</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-0.0332446147700013</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.00937717650784742</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>0.378097232299442</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>0.204919230346524</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>0.189167606171193</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0.239959840162856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>0.185955605881126</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>0.142647915223824</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.0121396505722817</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.0159294401376966</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.0128539066790523</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.0217074337461286</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.0151304626694743</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.0111464545769639</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>0.120713048295741</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>0.734967675977617</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>82.19</t>
+          <t>0.821881057668725</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>116.9</t>
+          <t>1.16899278891417</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>98.81</t>
+          <t>0.988141986347922</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>88.29</t>
+          <t>0.882934341134675</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>90.77</t>
+          <t>0.907666444431262</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>0.792039359861365</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>0.712948078704306</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>54.51</t>
+          <t>0.545071747761396</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>0.48410433178339</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>0.464150507668583</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>0.43279320343143</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>0.442873766900103</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.17</t>
+          <t>0.421669546253962</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>57.22</t>
+          <t>0.572248043151312</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>339.76</t>
+          <t>3.39763490201523</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>302.41</t>
+          <t>3.02409447146571</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>289.29</t>
+          <t>2.89285838584991</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>265.18</t>
+          <t>2.65179269382631</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>278.15</t>
+          <t>2.78146453212023</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>226.35</t>
+          <t>2.26346724412496</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>224.51</t>
+          <t>2.24507760260243</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>159.65</t>
+          <t>1.59653569129951</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>120.82</t>
+          <t>1.20820900117931</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>114.67</t>
+          <t>1.14665020712441</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>132.67</t>
+          <t>1.32667465106591</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>139.88</t>
+          <t>1.39881104542598</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>129.81</t>
+          <t>1.29808207021477</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>107.86</t>
+          <t>1.07860225444889</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>116.94</t>
+          <t>1.16938245114768</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>54.51</t>
+          <t>0.545111750284237</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>0.480593865830055</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.17</t>
+          <t>0.771721096822131</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>0.66162738455826</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>64.39</t>
+          <t>0.643933078935662</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>0.814335881856883</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>76.82</t>
+          <t>0.768209965120453</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>0.743057286149437</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>56.56</t>
+          <t>0.565615949806007</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>0.488303031631552</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>0.454913034544741</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>0.406670426218463</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>0.401695445626175</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>0.349595239979575</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>0.422841582729855</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>0.394333832495923</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>0.402671795761599</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>63.13</t>
+          <t>0.631274103063981</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>0.464936690299324</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>0.370518944193548</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>0.353556212701359</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>0.276135504781989</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>0.213520601873729</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>0.109361343369733</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>0.0878134663366563</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>0.0827022542811282</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>0.102724512765738</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>0.122562282084439</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>0.106370607381167</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>0.189486630689928</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>0.756663066001586</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>73.77</t>
+          <t>0.737735330792756</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>87.83</t>
+          <t>0.878270194213884</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>0.721260921889202</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>0.620794804032142</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>0.541126850829511</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.459176006226417</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>0.411060434129338</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>0.310377351239676</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>23.24</t>
+          <t>0.23240471952049</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>0.237544297923775</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>0.22553761770129</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>0.259679528418906</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>0.368853525521156</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>0.481463400521015</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>172.3</t>
+          <t>1.7230467571865</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>160.6</t>
+          <t>1.60596718741066</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>168.27</t>
+          <t>1.6827204571937</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>174.44</t>
+          <t>1.74435660965051</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>157.67</t>
+          <t>1.57669417662424</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>145.12</t>
+          <t>1.45120601262837</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>157.23</t>
+          <t>1.57225020833787</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>125.78</t>
+          <t>1.25782568090395</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>121.72</t>
+          <t>1.21716635105568</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>121.87</t>
+          <t>1.21869389444963</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>128.01</t>
+          <t>1.2800674302253</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>125.61</t>
+          <t>1.25613943626213</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>1.13799398954917</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>109.89</t>
+          <t>1.09890416483802</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>106.49</t>
+          <t>1.06491604713819</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>211.31</t>
+          <t>2.11311694774571</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>219.31</t>
+          <t>2.1930865533242</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>239.01</t>
+          <t>2.39006318957519</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>245.04</t>
+          <t>2.45042641661142</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>242.64</t>
+          <t>2.42637379708917</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>235.98</t>
+          <t>2.35978251865967</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>249.68</t>
+          <t>2.49678456505228</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>223.73</t>
+          <t>2.23725208639576</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>199.17</t>
+          <t>1.99169712170215</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>243.93</t>
+          <t>2.43928570021246</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>249.67</t>
+          <t>2.49674487147138</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>266.02</t>
+          <t>2.66020260399533</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>253.55</t>
+          <t>2.53549007094451</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>251.06</t>
+          <t>2.5105907582848</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>277.65</t>
+          <t>2.7765147312365</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>106.78</t>
+          <t>1.06779534725975</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>114.34</t>
+          <t>1.14335773214696</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>148.66</t>
+          <t>1.48661934935044</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>158.96</t>
+          <t>1.58960774754692</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>1.68400060976216</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>145.67</t>
+          <t>1.45672555461229</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>144.96</t>
+          <t>1.44961866119398</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>142.56</t>
+          <t>1.42560434003757</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>119.72</t>
+          <t>1.19720298582987</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>128.07</t>
+          <t>1.28072247915381</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>109.15</t>
+          <t>1.0915357890114</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>1.00198501699193</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>0.865351340713738</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>0.916029220510595</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>84.83</t>
+          <t>0.848264000173881</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>0.485973071432569</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>63.63</t>
+          <t>0.63627221908372</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>0.566587154393996</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>59.16</t>
+          <t>0.591638183387091</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>63.17</t>
+          <t>0.631687640913657</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>0.665065298124408</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>0.652766320611524</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>0.681703883113176</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>0.602916140636102</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>53.55</t>
+          <t>0.535466373457808</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>48.61</t>
+          <t>0.486053253882136</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>0.448615889046402</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>0.487831537143834</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>54.47</t>
+          <t>0.544737431098522</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>0.488586457919042</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>79.52</t>
+          <t>0.795221255336585</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0.759979368381815</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>102.53</t>
+          <t>1.02531931706818</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>111.59</t>
+          <t>1.11590990155146</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>1.12672718503817</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>108.54</t>
+          <t>1.08537690561834</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>0.862625621509125</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>74.35</t>
+          <t>0.74352730702762</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>93.08</t>
+          <t>0.93082079608101</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>104.54</t>
+          <t>1.04538671539577</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>83.91</t>
+          <t>0.839073889141431</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>0.8429336166687</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0.69996687412786</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>0.538046290338151</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>0.386715013645429</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>0.719937846423274</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>0.772222502298106</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>93.27</t>
+          <t>0.93265878492795</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>0.929969962410539</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>0.912872520793958</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>0.906978761458192</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>80.67</t>
+          <t>0.806726689736384</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>0.755764988706686</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>0.584716910957349</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>0.484697308414089</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>0.475022868706755</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>0.454280814600257</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>52.58</t>
+          <t>0.525815995415318</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>51.74</t>
+          <t>0.517392131237387</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>66.65</t>
+          <t>0.666459792558273</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>0.409753222384928</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>60.23</t>
+          <t>0.602312622366925</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.29</t>
+          <t>0.792902633759569</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>83.97</t>
+          <t>0.839679087760184</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>0.732976286348281</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>63.76</t>
+          <t>0.637604003066518</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>0.654987391210822</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>73.25</t>
+          <t>0.73254576533654</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>0.685821567674411</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>0.590887825762677</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>0.579799983025304</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>66.27</t>
+          <t>0.662662370608868</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>84.05</t>
+          <t>0.840457080955203</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>0.89673226431972</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>83.35</t>
+          <t>0.833545692242574</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>83.62</t>
+          <t>0.836248843145206</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>0.879621579587148</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>107.43</t>
+          <t>1.07429611653861</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>125.49</t>
+          <t>1.25488412726692</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>135.17</t>
+          <t>1.35166389099253</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>125.85</t>
+          <t>1.25853867245394</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>123.81</t>
+          <t>1.23813445357225</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>119.81</t>
+          <t>1.19810468686527</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>1.04616195625613</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>104.27</t>
+          <t>1.04265837923484</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>100.01</t>
+          <t>1.00013098531942</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>93.67</t>
+          <t>0.936736349143361</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>97.19</t>
+          <t>0.971947917187258</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>113.69</t>
+          <t>1.13688030034151</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>126.31</t>
+          <t>1.26312775886676</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>274.33</t>
+          <t>2.74334813719617</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>250.56</t>
+          <t>2.50556247968519</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>2.56504981798156</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>201.12</t>
+          <t>2.01119518633754</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>190.13</t>
+          <t>1.90132295153037</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>188.33</t>
+          <t>1.88329859505659</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>191.18</t>
+          <t>1.91184254731119</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>182.48</t>
+          <t>1.82483534467417</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>154.36</t>
+          <t>1.54360343516806</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>1.9550277415928</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>191.63</t>
+          <t>1.91634838777126</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>183.37</t>
+          <t>1.83369924211977</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>1.97998410290901</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>174.68</t>
+          <t>1.74680140693664</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>183.51</t>
+          <t>1.83513021648075</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>0.233971258427972</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>0.435689116290539</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>0.728548103903838</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>0.752648036759895</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>0.677403533544795</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>0.637661193045775</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>0.803540102753357</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>0.680992279643819</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>60.43</t>
+          <t>0.604334901737478</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>0.566811045066922</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>0.497751736861445</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>0.54814201472497</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>77.54</t>
+          <t>0.775447443781672</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>52.66</t>
+          <t>0.526574012060653</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>77.02</t>
+          <t>0.770193265053003</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>311.4</t>
+          <t>3.11403950930426</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>2.80401067333916</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>281.78</t>
+          <t>2.81783618165494</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>279.57</t>
+          <t>2.79570126365652</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>285.8</t>
+          <t>2.85795132836326</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>339.55</t>
+          <t>3.39546888201591</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>346.11</t>
+          <t>3.46111386143455</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>358.85</t>
+          <t>3.58852846340233</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>335.75</t>
+          <t>3.35746843919992</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>336.82</t>
+          <t>3.36822069135611</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>318.72</t>
+          <t>3.18718557189767</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>290.01</t>
+          <t>2.9001118097146</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>244.72</t>
+          <t>2.44718002231272</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>200.35</t>
+          <t>2.0035294685311</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>239.85</t>
+          <t>2.39849879136321</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>350.64</t>
+          <t>3.50636711200005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>378.25</t>
+          <t>3.78254138710177</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>412.47</t>
+          <t>4.1247222389742</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>381.82</t>
+          <t>3.81823668706722</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>3.57999348441933</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>347.8</t>
+          <t>3.47798756123376</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>302.94</t>
+          <t>3.02944540637662</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>303.87</t>
+          <t>3.03866735789028</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>307.08</t>
+          <t>3.07082410174931</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>324.03</t>
+          <t>3.24033662785243</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>338.86</t>
+          <t>3.38861614998741</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>361.39</t>
+          <t>3.61385165483009</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>376.35</t>
+          <t>3.76345894741322</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>388.34</t>
+          <t>3.88341934561638</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>393.28</t>
+          <t>3.93282558946196</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>174.53</t>
+          <t>1.74529671040559</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>157.03</t>
+          <t>1.57025120080309</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>217.67</t>
+          <t>2.17665836499838</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>194.74</t>
+          <t>1.94735789599233</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>162.86</t>
+          <t>1.62858948277815</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>146.96</t>
+          <t>1.46962922288181</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>0.850695590454234</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>104.43</t>
+          <t>1.04431668450707</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>76.07</t>
+          <t>0.760738754394388</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>131.43</t>
+          <t>1.31429723532588</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>1.3062714187878</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>137.21</t>
+          <t>1.37206531874469</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>124.74</t>
+          <t>1.24744240678442</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>100.03</t>
+          <t>1.00026249210483</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>125.97</t>
+          <t>1.25972200215621</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-20.18</t>
+          <t>-0.201793083948792</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-0.159359139533918</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>0.253521448859265</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.0184108780231036</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-0.0389599047380286</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.0129607754227443</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-0.0904089651517177</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-18.91</t>
+          <t>-0.189068491207959</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-17.7</t>
+          <t>-0.177037433307046</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-16.52</t>
+          <t>-0.16522613358896</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-0.141081697886203</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>-0.146621432384742</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>-0.141851987797291</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-21.11</t>
+          <t>-0.211089875196281</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-18.33</t>
+          <t>-0.183341053761038</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>0.918035849563623</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>0.82373149678221</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>81.63</t>
+          <t>0.816344641537663</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>0.765598531635317</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>0.904729964724785</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>101.65</t>
+          <t>1.01650943982963</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>160.34</t>
+          <t>1.60343008360202</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>166.01</t>
+          <t>1.66010418023904</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>178.32</t>
+          <t>1.78324752944416</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>196.17</t>
+          <t>1.96169804123581</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>186.44</t>
+          <t>1.86435095840507</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>194.88</t>
+          <t>1.94881362433203</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>199.56</t>
+          <t>1.99563866796617</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>172.1</t>
+          <t>1.72101366013013</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>198.4</t>
+          <t>1.98403085848969</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>115.25</t>
+          <t>1.15248208965952</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>1.11123003160034</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>146.1</t>
+          <t>1.46103615152928</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>125.49</t>
+          <t>1.25492278898807</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>1.29902764638293</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>1.25795811520505</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>116.62</t>
+          <t>1.16623263471371</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>1.20877930154882</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>113.93</t>
+          <t>1.13926865791158</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>116.65</t>
+          <t>1.16650392853433</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>119.74</t>
+          <t>1.197376257165</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>141.83</t>
+          <t>1.41830889164725</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>143.11</t>
+          <t>1.43113466664151</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>130.56</t>
+          <t>1.30556878309733</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>160.02</t>
+          <t>1.60018119949806</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>169.02</t>
+          <t>1.69018552013262</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>175.83</t>
+          <t>1.75831189478294</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>204.49</t>
+          <t>2.04489973658919</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>1.43204734296871</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>138.59</t>
+          <t>1.3858844350168</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>102.62</t>
+          <t>1.02618611737625</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>0.938985458178828</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>164.01</t>
+          <t>1.64007558409284</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>156.41</t>
+          <t>1.56413747813495</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>209.43</t>
+          <t>2.09434958027966</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>167.15</t>
+          <t>1.67151998580422</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>182.01</t>
+          <t>1.82011569354925</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>167.96</t>
+          <t>1.67959014333771</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>147.91</t>
+          <t>1.47907100664282</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>179.24</t>
+          <t>1.79242627268658</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>127.21</t>
+          <t>1.27207936974287</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>117.3</t>
+          <t>1.17297772721492</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>137.43</t>
+          <t>1.37433492742503</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>152.68</t>
+          <t>1.52677583379203</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>163.48</t>
+          <t>1.63481390670779</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>136.18</t>
+          <t>1.36175107575546</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>143.31</t>
+          <t>1.43307431462201</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>135.07</t>
+          <t>1.35068391872688</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>114.69</t>
+          <t>1.14692212334875</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>107.29</t>
+          <t>1.07288088662716</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>1.00729961440337</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>1.0209993685266</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>0.831886798322389</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>0.5873557469352</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>0.569404178170184</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>471.07</t>
+          <t>4.71065742295972</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>442.27</t>
+          <t>4.42272685918784</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>458.76</t>
+          <t>4.58758460350872</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>454.31</t>
+          <t>4.54306571376076</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>486.77</t>
+          <t>4.86769353296403</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>462.98</t>
+          <t>4.6298120173577</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>450.11</t>
+          <t>4.50105330681854</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>438.83</t>
+          <t>4.38825443628716</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>364.85</t>
+          <t>3.64847749852633</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>2.79000511552209</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>285.12</t>
+          <t>2.85123595654793</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>258.2</t>
+          <t>2.5819903198507</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>205.12</t>
+          <t>2.05120179735314</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>2.0968004548875</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>154.86</t>
+          <t>1.54864148318025</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>65.51</t>
+          <t>0.655145789572406</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.704173436422127</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>92.19</t>
+          <t>0.921869795486186</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>0.822291307927175</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>82.38</t>
+          <t>0.823839794934956</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>81.95</t>
+          <t>0.819467105290676</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>75.94</t>
+          <t>0.759417965375601</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>0.751024954771597</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>0.566334367095443</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>65.59</t>
+          <t>0.655929392159982</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>0.72646051225672</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>73.97</t>
+          <t>0.739679520682853</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>0.784330522524147</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>0.281498139750258</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>29.56</t>
+          <t>0.295627660911696</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>0.468812867103796</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>0.441463234108962</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>68.16</t>
+          <t>0.681558279987438</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>0.55486396438875</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>0.551488671021225</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>0.417564304726777</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>0.398151507785851</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>0.342764428639234</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>0.240169720399286</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>0.202256783281423</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.166510729939475</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>16.94</t>
+          <t>0.16942295928114</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>0.13699334143949</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>0.210684766503654</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>0.375677830450325</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>198.05</t>
+          <t>1.98048338908595</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>168.87</t>
+          <t>1.68871760730029</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>161.01</t>
+          <t>1.61011414534619</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>158.98</t>
+          <t>1.58975378916442</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>141.36</t>
+          <t>1.41364704400101</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>183.21</t>
+          <t>1.83207777331968</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>202.24</t>
+          <t>2.02238392835983</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>243.4</t>
+          <t>2.43396892207185</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>230.32</t>
+          <t>2.3032172668454</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>213.16</t>
+          <t>2.13161437142198</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>238.7</t>
+          <t>2.38696322563236</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>257.17</t>
+          <t>2.57165130531147</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>253.3</t>
+          <t>2.53299105306271</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>101.85</t>
+          <t>1.01851696538719</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>124.24</t>
+          <t>1.24235051750131</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>84.98</t>
+          <t>0.849759670271585</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>0.718132808960954</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>0.948982120968161</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>102.83</t>
+          <t>1.02833015520434</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>108.33</t>
+          <t>1.08334854809121</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>0.977844009861518</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>0.907311934757038</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>95.49</t>
+          <t>0.954939056216842</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>0.939788393159542</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>0.974040929650107</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>0.998995378927668</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>106.56</t>
+          <t>1.06560584104724</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>130.6</t>
+          <t>1.30597424630462</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>129.49</t>
+          <t>1.29485484419751</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>154.61</t>
+          <t>1.54609552742734</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>100.77</t>
+          <t>1.00766503642045</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>1.04447962763363</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>1.03992323333288</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>0.921466478596018</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>86.25</t>
+          <t>0.862530500822946</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>0.679645763195824</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>0.605839828196716</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>0.559195174641366</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>0.498948898348644</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.463087109392907</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>0.460208895858219</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>49.83</t>
+          <t>0.498297098837098</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>0.613505976221917</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>70.88</t>
+          <t>0.708791232493141</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>74.61</t>
+          <t>0.746147555681787</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>0.071585337751725</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>0.130711549371719</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.13334783120386</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12.94</t>
+          <t>0.129442913175889</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>0.114035073704453</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>0.0883252987862739</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>0.0997842379795852</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>0.108289798521977</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>0.137224249297189</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>0.204384491380075</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>0.186607328240815</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.181787673116957</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>0.258513942299327</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>0.275029858079926</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>0.299751575047654</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0.280029253575377</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>0.338064464824136</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>0.366797251649356</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>0.367976766135891</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>0.378231707750665</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.368448490611619</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>0.382754629702732</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>0.401223122608819</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>39.74</t>
+          <t>0.397413041163594</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>0.424995763760342</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>0.420076325434641</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.424803422114955</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>0.499663281138854</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>0.513960764524065</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>0.535978053082486</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
